--- a/spec-tech/ig/StructureDefinition-xdmActorXdsCore.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorXdsCore.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmActorXdsCore.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorXdsCore.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,7 @@
   </si>
   <si>
     <t>Cet attribut représente un acteur (humain ou système) ayant contribué au document. Pour les documents d’expression personnelle du patient, cette métadonnée fait référence au patient. 
-Type XCN de HL7 v2.5</t>
+Type xcn de HL7 v2.5</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -257,7 +257,7 @@
     <t>ActorXDS</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN1</t>
+    <t>xdmActorXdsCore.xcn1</t>
   </si>
   <si>
     <t>1</t>
@@ -273,7 +273,7 @@
     <t>author/assignedAuthor/id@extension</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN2</t>
+    <t>xdmActorXdsCore.xcn2</t>
   </si>
   <si>
     <t>Nom d'exercice du professionnel, nom du patient, nom du système.</t>
@@ -282,7 +282,7 @@
     <t>author/assignedAuthor/assignedPerson/name/family</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN3</t>
+    <t>xdmActorXdsCore.xcn3</t>
   </si>
   <si>
     <t>Prénom usuel de la personne (par défaut le premier prénom), nom du modèle pour les dispositifs ou dénomination pour les autres systèmes.</t>
@@ -291,7 +291,7 @@
     <t>author/assignedAuthor/assignedPerson/name/given</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN9</t>
+    <t>xdmActorXdsCore.xcn9</t>
   </si>
   <si>
     <t xml:space="preserve">Base
@@ -304,13 +304,13 @@
     <t>NA</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN9.composant1</t>
+    <t>xdmActorXdsCore.xcn9.composant1</t>
   </si>
   <si>
     <t>Vide, pas de valeur</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN9.composant2</t>
+    <t>xdmActorXdsCore.xcn9.composant2</t>
   </si>
   <si>
     <t>Valeur de Universal ID</t>
@@ -319,7 +319,7 @@
     <t>author/assignedAuthor/id@root</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN9.composant3</t>
+    <t>xdmActorXdsCore.xcn9.composant3</t>
   </si>
   <si>
     <t>Valeur de Universal ID type (ID). Valeur fixée à 'ISO'</t>
@@ -328,7 +328,7 @@
     <t>ISO</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN10</t>
+    <t>xdmActorXdsCore.xcn10</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -338,7 +338,7 @@
     <t>Type de nom : 'D' pour les personnes physiques, 'U', pour les systèmes.</t>
   </si>
   <si>
-    <t>xdmActorXdsCore.XCN13</t>
+    <t>xdmActorXdsCore.xcn13</t>
   </si>
   <si>
     <t>Type d’identifiant</t>
@@ -649,8 +649,8 @@
   <dimension ref="A1:AK11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="30.14453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="30.14453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="29.58203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="29.58203125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -680,7 +680,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="30.14453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.58203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
